--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2891-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2891-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2E5D966-72D1-42FF-ACDD-02600E537999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48E15EFB-6E35-4814-A8F1-669247687960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{77F9177B-E9B2-4F6F-8C7E-6F30A0D9FA9D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E654389C-183C-4DFE-AF42-4A72FB355F7A}"/>
   </bookViews>
   <sheets>
     <sheet name="2891-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1592,27 +1592,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F01EDD8-8D26-4F7F-9B91-36C91BCDFF6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6DCB6A6-19A5-4E60-A122-5BF648771ADD}">
   <dimension ref="A1:X40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1646,7 +1645,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1682,7 +1681,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1734,7 +1733,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1802,7 +1801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1874,7 +1873,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1946,7 +1945,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2018,7 +2017,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2090,7 +2089,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2162,7 +2161,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2234,7 +2233,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2306,7 +2305,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2378,7 +2377,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2450,7 +2449,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="42">
         <v>2015</v>
       </c>
@@ -2522,7 +2521,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="44"/>
       <c r="B15" s="45"/>
       <c r="C15" s="18" t="s">
@@ -2550,7 +2549,7 @@
       <c r="W15" s="51"/>
       <c r="X15" s="47"/>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2014</v>
       </c>
@@ -2622,7 +2621,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="42">
         <v>2013</v>
       </c>
@@ -2694,7 +2693,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="44"/>
       <c r="B18" s="45"/>
       <c r="C18" s="18" t="s">
@@ -2722,7 +2721,7 @@
       <c r="W18" s="51"/>
       <c r="X18" s="47"/>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="52">
         <v>2012</v>
       </c>
@@ -2794,7 +2793,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="54"/>
       <c r="B20" s="55"/>
       <c r="C20" s="21" t="s">
@@ -2822,7 +2821,7 @@
       <c r="W20" s="61"/>
       <c r="X20" s="57"/>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="42">
         <v>2011</v>
       </c>
@@ -2894,7 +2893,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="44"/>
       <c r="B22" s="45"/>
       <c r="C22" s="18" t="s">
@@ -2922,7 +2921,7 @@
       <c r="W22" s="51"/>
       <c r="X22" s="47"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="52">
         <v>2010</v>
       </c>
@@ -2994,7 +2993,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="54"/>
       <c r="B24" s="55"/>
       <c r="C24" s="21" t="s">
@@ -3022,7 +3021,7 @@
       <c r="W24" s="61"/>
       <c r="X24" s="57"/>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="42">
         <v>2009</v>
       </c>
@@ -3094,7 +3093,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="44"/>
       <c r="B26" s="45"/>
       <c r="C26" s="18" t="s">
@@ -3122,7 +3121,7 @@
       <c r="W26" s="51"/>
       <c r="X26" s="47"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="52">
         <v>2008</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="54"/>
       <c r="B28" s="55"/>
       <c r="C28" s="21" t="s">
@@ -3222,7 +3221,7 @@
       <c r="W28" s="61"/>
       <c r="X28" s="57"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="42">
         <v>2007</v>
       </c>
@@ -3294,7 +3293,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="44"/>
       <c r="B30" s="45"/>
       <c r="C30" s="18" t="s">
@@ -3322,7 +3321,7 @@
       <c r="W30" s="51"/>
       <c r="X30" s="47"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2006</v>
       </c>
@@ -3394,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="42">
         <v>2005</v>
       </c>
@@ -3466,7 +3465,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="44"/>
       <c r="B33" s="45"/>
       <c r="C33" s="18" t="s">
@@ -3494,7 +3493,7 @@
       <c r="W33" s="51"/>
       <c r="X33" s="47"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="52">
         <v>2004</v>
       </c>
@@ -3566,7 +3565,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="54"/>
       <c r="B35" s="55"/>
       <c r="C35" s="21" t="s">
@@ -3594,7 +3593,7 @@
       <c r="W35" s="61"/>
       <c r="X35" s="57"/>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="42">
         <v>2003</v>
       </c>
@@ -3666,7 +3665,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="44"/>
       <c r="B37" s="45"/>
       <c r="C37" s="18" t="s">
@@ -3694,7 +3693,7 @@
       <c r="W37" s="51"/>
       <c r="X37" s="47"/>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="52">
         <v>2002</v>
       </c>
@@ -3766,7 +3765,7 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="54"/>
       <c r="B39" s="55"/>
       <c r="C39" s="21" t="s">
@@ -3794,7 +3793,7 @@
       <c r="W39" s="61"/>
       <c r="X39" s="57"/>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="40" t="s">
         <v>63</v>
       </c>
